--- a/data/trans_dic/P19C06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,78</t>
+          <t>0,81; 2,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,26; 1,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,36</t>
+          <t>0,4; 2,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,49</t>
+          <t>0,67; 5,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,57</t>
+          <t>0,4; 1,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,07</t>
+          <t>0,7; 2,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,96</t>
+          <t>0,78; 2,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,53</t>
+          <t>0,89; 2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,74</t>
+          <t>0,72; 1,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,64</t>
+          <t>0,62; 1,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,31</t>
+          <t>0,83; 2,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,2</t>
+          <t>0,99; 3,06</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,47</t>
+          <t>0,48; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,77</t>
+          <t>0,65; 1,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,05</t>
+          <t>0,82; 2,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,16</t>
+          <t>0,36; 1,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,8</t>
+          <t>0,64; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,28</t>
+          <t>0,99; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,76</t>
+          <t>0,7; 1,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,19</t>
+          <t>0,48; 1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,45</t>
+          <t>0,69; 1,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,7</t>
+          <t>0,93; 1,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,73</t>
+          <t>0,88; 1,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,02</t>
+          <t>0,48; 1,0</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,57</t>
+          <t>0,22; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,71</t>
+          <t>0,41; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,99</t>
+          <t>0,2; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,58</t>
+          <t>0,25; 1,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,42</t>
+          <t>0,73; 3,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,06</t>
+          <t>0,56; 3,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,1</t>
+          <t>0,66; 3,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,43</t>
+          <t>0,77; 2,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,27</t>
+          <t>0,69; 2,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,37</t>
+          <t>0,76; 2,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,09</t>
+          <t>0,63; 2,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,65</t>
+          <t>0,64; 1,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,56</t>
+          <t>0,76; 1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,44</t>
+          <t>0,64; 1,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,66</t>
+          <t>0,83; 1,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,38</t>
+          <t>0,49; 1,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,57</t>
+          <t>0,79; 1,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,92</t>
+          <t>1,08; 1,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,79</t>
+          <t>0,99; 1,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,45</t>
+          <t>0,79; 1,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,45</t>
+          <t>0,85; 1,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,53</t>
+          <t>0,93; 1,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,58</t>
+          <t>0,97; 1,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,27</t>
+          <t>0,72; 1,21</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5123; 19178</t>
+          <t>5609; 18346</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2005; 12246</t>
+          <t>2009; 12156</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1814; 10811</t>
+          <t>1813; 10972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2917; 26615</t>
+          <t>3236; 25485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3967; 15086</t>
+          <t>3863; 15404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8118; 23411</t>
+          <t>7947; 24612</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5309; 18920</t>
+          <t>4996; 18504</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6402; 18270</t>
+          <t>6422; 18078</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11698; 28721</t>
+          <t>11864; 28492</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12133; 31365</t>
+          <t>11896; 29481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9434; 25344</t>
+          <t>9083; 24444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12384; 38615</t>
+          <t>11976; 36879</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5811; 19278</t>
+          <t>6352; 19408</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9825; 29940</t>
+          <t>10975; 30825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13736; 34806</t>
+          <t>13831; 35089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7939; 25818</t>
+          <t>8123; 25459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8792; 24762</t>
+          <t>8745; 25892</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15787; 36235</t>
+          <t>15726; 36108</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12184; 30061</t>
+          <t>12033; 30005</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10699; 26114</t>
+          <t>10574; 25752</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17729; 39003</t>
+          <t>18628; 39169</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29257; 55720</t>
+          <t>30515; 59159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31075; 58857</t>
+          <t>30075; 58626</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21655; 45389</t>
+          <t>21302; 44270</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1009; 11579</t>
+          <t>1004; 11757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2137; 11962</t>
+          <t>1810; 12320</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1046; 9933</t>
+          <t>989; 9164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1429; 9944</t>
+          <t>1576; 9870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3019; 13961</t>
+          <t>2970; 15201</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2191; 12969</t>
+          <t>2353; 13270</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3311; 15750</t>
+          <t>3365; 16365</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5026; 15812</t>
+          <t>5034; 15050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6178; 19527</t>
+          <t>5908; 20054</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6226; 20525</t>
+          <t>6548; 21539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6180; 21085</t>
+          <t>6358; 22594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8438; 21157</t>
+          <t>8153; 21916</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18164; 38256</t>
+          <t>18548; 38698</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18672; 41948</t>
+          <t>18492; 42082</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20970; 44101</t>
+          <t>21956; 45097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16883; 46117</t>
+          <t>16393; 44238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21919; 43006</t>
+          <t>21592; 42782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33776; 60274</t>
+          <t>33842; 59747</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26591; 51009</t>
+          <t>28184; 54103</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28596; 51838</t>
+          <t>28095; 50838</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44581; 75159</t>
+          <t>43972; 74330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56933; 92352</t>
+          <t>56535; 94476</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53457; 87177</t>
+          <t>53443; 88279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50802; 87861</t>
+          <t>49484; 83855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,66</t>
+          <t>0,82; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,56</t>
+          <t>0,25; 1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,4</t>
+          <t>0,36; 2,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,26</t>
+          <t>0,43; 3,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,61</t>
+          <t>0,47; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,18</t>
+          <t>0,72; 2,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,9</t>
+          <t>0,84; 3,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,51</t>
+          <t>0,84; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,73</t>
+          <t>0,72; 1,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,55</t>
+          <t>0,6; 1,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,23</t>
+          <t>0,83; 2,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,06</t>
+          <t>0,87; 2,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,48</t>
+          <t>0,45; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,83</t>
+          <t>0,63; 1,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,07</t>
+          <t>0,82; 2,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,14</t>
+          <t>0,37; 1,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,89</t>
+          <t>0,66; 1,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,27</t>
+          <t>1,0; 2,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,76</t>
+          <t>0,72; 1,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,17</t>
+          <t>0,57; 1,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,46</t>
+          <t>0,68; 1,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,81</t>
+          <t>0,94; 1,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,72</t>
+          <t>0,9; 1,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,0</t>
+          <t>0,56; 1,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,61</t>
+          <t>0,33; 2,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,79</t>
+          <t>0,45; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,21; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,56</t>
+          <t>0,22; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,72</t>
+          <t>0,73; 3,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,13</t>
+          <t>0,53; 3,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,22</t>
+          <t>0,73; 3,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,31</t>
+          <t>0,81; 2,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,33</t>
+          <t>0,7; 2,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,49</t>
+          <t>0,74; 2,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,24</t>
+          <t>0,6; 1,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,71</t>
+          <t>0,65; 1,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,58</t>
+          <t>0,73; 1,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,45</t>
+          <t>0,63; 1,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,7</t>
+          <t>0,8; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,32</t>
+          <t>0,5; 1,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,56</t>
+          <t>0,79; 1,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,9</t>
+          <t>1,04; 1,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,89</t>
+          <t>0,97; 1,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,42</t>
+          <t>0,86; 1,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,43</t>
+          <t>0,86; 1,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,56</t>
+          <t>0,95; 1,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,6</t>
+          <t>0,95; 1,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,21</t>
+          <t>0,75; 1,2</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>18226</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5609; 18346</t>
+          <t>5666; 19236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2009; 12156</t>
+          <t>1966; 11767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1813; 10972</t>
+          <t>1633; 10987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3236; 25485</t>
+          <t>2331; 16825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3863; 15404</t>
+          <t>4497; 16039</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7947; 24612</t>
+          <t>8081; 22804</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4996; 18504</t>
+          <t>5351; 19193</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6422; 18078</t>
+          <t>6610; 17404</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11864; 28492</t>
+          <t>11938; 28918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11896; 29481</t>
+          <t>11457; 29585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9083; 24444</t>
+          <t>9094; 25738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11976; 36879</t>
+          <t>11559; 29976</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>32821</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6352; 19408</t>
+          <t>5915; 19768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10975; 30825</t>
+          <t>10607; 28898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13831; 35089</t>
+          <t>13858; 34846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8123; 25459</t>
+          <t>8044; 24043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8745; 25892</t>
+          <t>9103; 25566</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15726; 36108</t>
+          <t>15969; 35992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12033; 30005</t>
+          <t>12313; 30219</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10574; 25752</t>
+          <t>12070; 27863</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18628; 39169</t>
+          <t>18178; 38587</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30515; 59159</t>
+          <t>30953; 59900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30075; 58626</t>
+          <t>30780; 59037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21302; 44270</t>
+          <t>23827; 45491</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>14770</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1004; 11757</t>
+          <t>1496; 11219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1810; 12320</t>
+          <t>1977; 12248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>989; 9164</t>
+          <t>1045; 10003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1576; 9870</t>
+          <t>1511; 11338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2970; 15201</t>
+          <t>3000; 14382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2353; 13270</t>
+          <t>2254; 13447</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3365; 16365</t>
+          <t>3735; 16232</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5034; 15050</t>
+          <t>5854; 16861</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5908; 20054</t>
+          <t>6056; 20200</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6548; 21539</t>
+          <t>6370; 20505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6358; 22594</t>
+          <t>6034; 20092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8153; 21916</t>
+          <t>9262; 22420</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>65816</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18548; 38698</t>
+          <t>17947; 39477</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18492; 42082</t>
+          <t>18401; 42009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21956; 45097</t>
+          <t>21232; 45527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16393; 44238</t>
+          <t>17029; 39163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21592; 42782</t>
+          <t>21766; 43025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33842; 59747</t>
+          <t>32558; 61677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28184; 54103</t>
+          <t>27686; 52252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28095; 50838</t>
+          <t>31171; 52400</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43972; 74330</t>
+          <t>44777; 75670</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56535; 94476</t>
+          <t>57477; 92644</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53443; 88279</t>
+          <t>52326; 87450</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49484; 83855</t>
+          <t>52871; 84081</t>
         </is>
       </c>
     </row>
